--- a/artfynd/A 33857-2024 artfynd.xlsx
+++ b/artfynd/A 33857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96277344</v>
+        <v>101237322</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kohobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614338.4826714628</v>
+        <v>614212</v>
       </c>
       <c r="R2" t="n">
-        <v>7218202.619314483</v>
+        <v>7218016</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,37 +761,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jörgen Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96277347</v>
+        <v>96277348</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614083.0379787359</v>
+        <v>614083</v>
       </c>
       <c r="R3" t="n">
-        <v>7218158.57920537</v>
+        <v>7218157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +848,9 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,37 +896,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96277348</v>
+        <v>56824999</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614083.086589762</v>
+        <v>614350</v>
       </c>
       <c r="R4" t="n">
-        <v>7218157.313810361</v>
+        <v>7218141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,22 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,71 +978,57 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96277345</v>
+        <v>96277344</v>
       </c>
       <c r="B5" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614203.3283651848</v>
+        <v>614339</v>
       </c>
       <c r="R5" t="n">
-        <v>7218142.926382408</v>
+        <v>7218203</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,19 +1071,9 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,6 +1097,444 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96277345</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kohobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>614203</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7218143</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>101243000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kohobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>613965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7218145</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-05-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-05-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>56825000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kohobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>614351</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7218121</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96277347</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kohobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>614083</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7218158</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
